--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9256298535</v>
+        <v>46157.93074485266</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93074485266</v>
+        <v>46157.93157275661</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93157275661</v>
+        <v>46157.93394630286</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394630286</v>
+        <v>46157.93710649465</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93710649465</v>
+        <v>46158.28211559349</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211559349</v>
+        <v>46158.29667486457</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29667486457</v>
+        <v>46158.29807219872</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807219872</v>
+        <v>46158.33382396759</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382396759</v>
+        <v>46158.36849829336</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36849829336</v>
+        <v>46158.3728251172</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
